--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-coverage.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -845,7 +845,7 @@
   </si>
   <si>
     <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).  
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4B/datatypes.html#Duration).  
 Period（期間）は時間の範囲を指定する。使用状況は、範囲全体が適用されるか（たとえば、「患者はこの時間範囲で入院していた」）、範囲から1つの値が適用されるか（たとえば、「この2回の間に患者に投与する」）を指定する。  
 Period（期間）は、Duration（時間区間＝経過時間の測定値）には使用されない。 [Duration]（datatypes.html＃Duration）を参照のこと。  
 This is not a duration - that's a measure of time (a separate type), but a duration that occurs at a fixed value of time. A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times"). If duration is required, specify the type as Interval|Duration.  
